--- a/data/analysis_ministral_3_14b_qwen2_audio/multimodal_event_eval_ministral_3_14b_qwen2_audio_w2_5s_h2_5s.xlsx
+++ b/data/analysis_ministral_3_14b_qwen2_audio/multimodal_event_eval_ministral_3_14b_qwen2_audio_w2_5s_h2_5s.xlsx
@@ -109,7 +109,7 @@
     <t>sound: shout(0-240), visual: carrying(72-144), visual: physical_altercation(96-144), visual: physical_altercation(168-168), visual: running(72-168), visual: running(192-216), visual: running(192-216), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(192-216), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-120), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(168-168)</t>
   </si>
   <si>
-    <t>sound: shout(0-240), sound: impact(120-180), visual: carrying(120-120), visual: physical_altercation(72-72)</t>
+    <t>sound: shout(0-120), sound: shout(180-240), sound: impact(120-180), visual: carrying(120-120), visual: physical_altercation(72-72)</t>
   </si>
   <si>
     <t>sound: engine(0-60), sound: engine(180-240), sound: gunshot_or_explosion(60-120), sound: impact(120-180), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: gunshot_visible(168-168), visual: running(120-240), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(24-120), visual: vehicle_collision(216-240)</t>
@@ -121,7 +121,7 @@
     <t>sound: engine(0-60), sound: impact(60-120), sound: shout(120-240), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: enter_or_exit_vehicle(48-72), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(48-144), visual: suspicious_near_vehicle(0-0)</t>
   </si>
   <si>
-    <t>sound: shout(0-240), sound: impact(120-180), visual: carrying(144-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-120), visual: gunshot_visible(120-120), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(144-168), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(96-96)</t>
+    <t>sound: shout(0-120), sound: shout(180-240), sound: impact(120-180), visual: carrying(144-216), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-120), visual: gunshot_visible(120-120), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(144-168), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-60), sound: shout(60-180), sound: engine(180-240), visual: explosion_visible(24-240), visual: running(24-240), visual: running(120-240)</t>
